--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755604147_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008445755456178603</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44141546</v>
+        <v>4080666</v>
       </c>
       <c r="L2" t="n">
-        <v>23657763</v>
+        <v>1696630</v>
       </c>
       <c r="M2" t="n">
-        <v>5604074</v>
+        <v>351986</v>
       </c>
       <c r="N2" t="n">
-        <v>248359</v>
+        <v>5291</v>
       </c>
       <c r="O2" t="n">
-        <v>3316875</v>
+        <v>192966</v>
       </c>
       <c r="P2" t="n">
-        <v>1257265</v>
+        <v>48036</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999848008155823</v>
+        <v>0.9999628067016602</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8461499214172363</v>
+        <v>0.7306357026100159</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7200210690498352</v>
+        <v>0.5520269274711609</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6485683917999268</v>
+        <v>0.4168810248374939</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3188672363758087</v>
+        <v>0.06697807461023331</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7038654088973999</v>
+        <v>0.4679279625415802</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8170759677886963</v>
+        <v>0.6393972635269165</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002023579242838846</v>
       </c>
       <c r="C3" t="n">
-        <v>155</v>
+        <v>49</v>
       </c>
       <c r="D3" t="n">
-        <v>44141546</v>
+        <v>4080666</v>
       </c>
       <c r="E3" t="n">
-        <v>6116429</v>
+        <v>878720</v>
       </c>
       <c r="F3" t="n">
-        <v>165207</v>
+        <v>38805</v>
       </c>
       <c r="G3" t="n">
-        <v>11503</v>
+        <v>1815</v>
       </c>
       <c r="H3" t="n">
-        <v>10317</v>
+        <v>2789</v>
       </c>
       <c r="I3" t="n">
-        <v>706</v>
+        <v>146</v>
       </c>
       <c r="J3" t="n">
-        <v>100695236</v>
+        <v>10069384</v>
       </c>
       <c r="K3" t="n">
-        <v>105688160</v>
+        <v>9908586</v>
       </c>
       <c r="L3" t="n">
-        <v>122007400</v>
+        <v>11710790</v>
       </c>
       <c r="M3" t="n">
-        <v>151757916</v>
+        <v>14981130</v>
       </c>
       <c r="N3" t="n">
-        <v>162734132</v>
+        <v>16252317</v>
       </c>
       <c r="O3" t="n">
-        <v>157662923</v>
+        <v>15684644</v>
       </c>
       <c r="P3" t="n">
-        <v>161943915</v>
+        <v>16195104</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8750280737876892</v>
+        <v>0.8156454563140869</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7179174423217773</v>
+        <v>0.509745717048645</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5983758568763733</v>
+        <v>0.3734504282474518</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2773882448673248</v>
+        <v>0.0588032640516758</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6501660943031311</v>
+        <v>0.3769323527812958</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6498793363571167</v>
+        <v>0.2478573769330978</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03194845442669837</v>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>7435637</v>
+        <v>1358151</v>
       </c>
       <c r="E4" t="n">
-        <v>23657763</v>
+        <v>1696630</v>
       </c>
       <c r="F4" t="n">
-        <v>1610518</v>
+        <v>229143</v>
       </c>
       <c r="G4" t="n">
-        <v>67316</v>
+        <v>10731</v>
       </c>
       <c r="H4" t="n">
-        <v>167664</v>
+        <v>31426</v>
       </c>
       <c r="I4" t="n">
-        <v>14385</v>
+        <v>2295</v>
       </c>
       <c r="J4" t="n">
-        <v>964</v>
+        <v>236</v>
       </c>
       <c r="K4" t="n">
-        <v>8025977</v>
+        <v>1504424</v>
       </c>
       <c r="L4" t="n">
-        <v>9199280</v>
+        <v>1376825</v>
       </c>
       <c r="M4" t="n">
-        <v>3036609</v>
+        <v>492346</v>
       </c>
       <c r="N4" t="n">
-        <v>530520</v>
+        <v>73705</v>
       </c>
       <c r="O4" t="n">
-        <v>1395496</v>
+        <v>219418</v>
       </c>
       <c r="P4" t="n">
-        <v>281472</v>
+        <v>27091</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999924302101135</v>
+        <v>0.9999814033508301</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8603467345237732</v>
+        <v>0.7708038091659546</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7189677357673645</v>
+        <v>0.5300444960594177</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6224619746208191</v>
+        <v>0.3939723968505859</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2966849803924561</v>
+        <v>0.06262501329183578</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6759508848190308</v>
+        <v>0.417529821395874</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7239494919776917</v>
+        <v>0.3572352826595306</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>417903</v>
+        <v>109093</v>
       </c>
       <c r="E5" t="n">
-        <v>2507096</v>
+        <v>375800</v>
       </c>
       <c r="F5" t="n">
-        <v>5604074</v>
+        <v>351986</v>
       </c>
       <c r="G5" t="n">
-        <v>167536</v>
+        <v>19749</v>
       </c>
       <c r="H5" t="n">
-        <v>610649</v>
+        <v>78022</v>
       </c>
       <c r="I5" t="n">
-        <v>58121</v>
+        <v>7850</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6304317</v>
+        <v>922324</v>
       </c>
       <c r="L5" t="n">
-        <v>9295557</v>
+        <v>1631755</v>
       </c>
       <c r="M5" t="n">
-        <v>3761401</v>
+        <v>590538</v>
       </c>
       <c r="N5" t="n">
-        <v>646989</v>
+        <v>84687</v>
       </c>
       <c r="O5" t="n">
-        <v>1784706</v>
+        <v>318972</v>
       </c>
       <c r="P5" t="n">
-        <v>677348</v>
+        <v>145769</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999940991401672</v>
+        <v>0.9999856352806091</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9127053022384644</v>
+        <v>0.852171778678894</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8873364925384521</v>
+        <v>0.8167288303375244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9585891366004944</v>
+        <v>0.9340348243713379</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9928270578384399</v>
+        <v>0.9903513789176941</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9806274175643921</v>
+        <v>0.9672033190727234</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9941592216491699</v>
+        <v>0.9894700050354004</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>218</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>137216</v>
+        <v>22202</v>
       </c>
       <c r="E6" t="n">
-        <v>189465</v>
+        <v>25851</v>
       </c>
       <c r="F6" t="n">
-        <v>224765</v>
+        <v>27016</v>
       </c>
       <c r="G6" t="n">
-        <v>248359</v>
+        <v>5291</v>
       </c>
       <c r="H6" t="n">
-        <v>86518</v>
+        <v>8725</v>
       </c>
       <c r="I6" t="n">
-        <v>8807</v>
+        <v>844</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>33666</v>
+        <v>14095</v>
       </c>
       <c r="E7" t="n">
-        <v>353105</v>
+        <v>86352</v>
       </c>
       <c r="F7" t="n">
-        <v>947331</v>
+        <v>169108</v>
       </c>
       <c r="G7" t="n">
-        <v>251066</v>
+        <v>33437</v>
       </c>
       <c r="H7" t="n">
-        <v>3316875</v>
+        <v>192966</v>
       </c>
       <c r="I7" t="n">
-        <v>199453</v>
+        <v>15956</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>1555</v>
+        <v>883</v>
       </c>
       <c r="E8" t="n">
-        <v>33185</v>
+        <v>10102</v>
       </c>
       <c r="F8" t="n">
-        <v>88788</v>
+        <v>28274</v>
       </c>
       <c r="G8" t="n">
-        <v>33099</v>
+        <v>7973</v>
       </c>
       <c r="H8" t="n">
-        <v>520348</v>
+        <v>98456</v>
       </c>
       <c r="I8" t="n">
-        <v>1257265</v>
+        <v>48036</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
